--- a/WorkBot/refactor-experimental/data/orders/Hill & Markes/Hill & Markes_Triphammer_20260220.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Hill & Markes/Hill & Markes_Triphammer_20260220.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,6 +695,111 @@
         <v>23.44</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TS12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 12oz Square</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="E14" t="n">
+        <v>38.39</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TS16</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 16oz</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="E15" t="n">
+        <v>41.88</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TS8</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tamper Evident - 8oz</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="E16" t="n">
+        <v>76.58</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HIMF1824XC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bag - Poly (10x8x24, 1.25mil)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="E17" t="n">
+        <v>130.68</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6G063015</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bag Poly - 6x3x15 LW</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
